--- a/registrations.xlsx
+++ b/registrations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,116 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nandhu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>charan</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9392717561</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5 months</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>veesamvinaykumar@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nandhu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>charan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>9392717561</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dandiya</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5 months</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>veesamvinaykumar@gmail.com</t>
         </is>
       </c>
     </row>
